--- a/hpi_scraper/NewsAnnouncements/exa/exa_api_report.xlsx
+++ b/hpi_scraper/NewsAnnouncements/exa/exa_api_report.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>1.836 avg</t>
+          <t>1.995 avg</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">

--- a/hpi_scraper/NewsAnnouncements/exa/exa_api_report.xlsx
+++ b/hpi_scraper/NewsAnnouncements/exa/exa_api_report.xlsx
@@ -449,15 +449,15 @@
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="59" customWidth="1" min="5" max="5"/>
+    <col width="51" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="65" customWidth="1" min="13" max="13"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="72" customWidth="1" min="12" max="12"/>
+    <col width="72" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -556,7 +556,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Search requests consume Exa account credits based on plan</t>
+          <t>1 Exa web/news discovery request for Sea Limited.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -564,15 +564,11 @@
           <t>Not returned in response headers</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -586,17 +582,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 articles/events returned.</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Y - source_publisher</t>
+          <t>Minor - publisher names were not consistently normalized by the provider.</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Exa is used for web/news discovery with last-12-month filtering where provider dates are available.</t>
+          <t>Useful for broad web discovery and deeper article text. Keep alongside Google News RSS/Tavily for coverage checks.</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
